--- a/sheets/대금율보/검수/영천 아리랑.xlsx
+++ b/sheets/대금율보/검수/영천 아리랑.xlsx
@@ -2454,7 +2454,7 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 潢</t>
         </is>
       </c>
@@ -2466,7 +2466,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–‹
+–
 無</t>
         </is>
       </c>
@@ -2516,8 +2516,7 @@
         <is>
           <t xml:space="preserve">–
 –
-浹
-‹</t>
+浹</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -2598,7 +2597,7 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -2620,7 +2619,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 浹</t>
         </is>
       </c>
@@ -2636,23 +2635,17 @@
         <is>
           <t xml:space="preserve">潢ㅅ
 無
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -2664,8 +2657,7 @@
         <is>
           <t xml:space="preserve">潢
 浹)
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -2736,7 +2728,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–‹
+–
 㳞</t>
         </is>
       </c>
@@ -2773,7 +2765,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–‹
+–
 浹</t>
         </is>
       </c>
@@ -2795,7 +2787,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–‹
+–
 浹</t>
         </is>
       </c>
@@ -2873,7 +2865,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–‹
+–
 無</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/영천 아리랑.xlsx
+++ b/sheets/대금율보/검수/영천 아리랑.xlsx
@@ -2374,20 +2374,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2912,6 +2912,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>